--- a/XBRL-template-MFRS/Company/04-SOPL-Nature.xlsx
+++ b/XBRL-template-MFRS/Company/04-SOPL-Nature.xlsx
@@ -691,8 +691,14 @@
           <t>Other income</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n"/>
-      <c r="C8" s="30" t="n"/>
+      <c r="B8" s="30">
+        <f>'SOPL-Analysis-Nature'!B83</f>
+        <v/>
+      </c>
+      <c r="C8" s="30">
+        <f>'SOPL-Analysis-Nature'!C83</f>
+        <v/>
+      </c>
       <c r="D8" s="34" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="10">
@@ -757,8 +763,14 @@
           <t>Other expenses, by nature</t>
         </is>
       </c>
-      <c r="B14" s="30" t="n"/>
-      <c r="C14" s="30" t="n"/>
+      <c r="B14" s="30">
+        <f>'SOPL-Analysis-Nature'!B128</f>
+        <v/>
+      </c>
+      <c r="C14" s="30">
+        <f>'SOPL-Analysis-Nature'!C128</f>
+        <v/>
+      </c>
       <c r="D14" s="34" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="10">
@@ -768,11 +780,11 @@
         </is>
       </c>
       <c r="B15" s="28">
-        <f>1*B7+1*B8+1*B9+1*B10+-1*B11+-1*B12+-1*B13+-1*B14</f>
+        <f>1*B7+1*B8+-1*B9+1*B10+-1*B11+-1*B12+-1*B13+-1*B14</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>1*C7+1*C8+1*C9+1*C10+-1*C11+-1*C12+-1*C13+-1*C14</f>
+        <f>1*C7+1*C8+-1*C9+1*C10+-1*C11+-1*C12+-1*C13+-1*C14</f>
         <v/>
       </c>
       <c r="D15" s="33" t="n"/>
@@ -783,8 +795,14 @@
           <t>Finance income</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n"/>
-      <c r="C16" s="30" t="n"/>
+      <c r="B16" s="30">
+        <f>'SOPL-Analysis-Nature'!B132</f>
+        <v/>
+      </c>
+      <c r="C16" s="30">
+        <f>'SOPL-Analysis-Nature'!C132</f>
+        <v/>
+      </c>
       <c r="D16" s="34" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="10">
@@ -814,11 +832,11 @@
         </is>
       </c>
       <c r="B19" s="28">
-        <f>1*B15+1*B16+-1*B17+1*B18</f>
+        <f>1*B7+1*B8+-1*B9+1*B10+-1*B11+-1*B12+-1*B13+-1*B14+1*B16+-1*B17+1*B18</f>
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>1*C15+1*C16+-1*C17+1*C18</f>
+        <f>1*C7+1*C8+-1*C9+1*C10+-1*C11+-1*C12+-1*C13+-1*C14+1*C16+-1*C17+1*C18</f>
         <v/>
       </c>
       <c r="D19" s="33" t="n"/>
@@ -1227,8 +1245,14 @@
           <t>Revenue from sale of goods</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n"/>
-      <c r="C16" s="37" t="n"/>
+      <c r="B16" s="37">
+        <f>1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="37">
+        <f>1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15</f>
+        <v/>
+      </c>
       <c r="D16" s="38" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="10">
@@ -1257,14 +1281,8 @@
           <t>Total revenue from rendering of telecommunication services</t>
         </is>
       </c>
-      <c r="B19" s="28">
-        <f>1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="28">
-        <f>1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C18</f>
-        <v/>
-      </c>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
       <c r="D19" s="33" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="10">
@@ -1333,8 +1351,14 @@
           <t>Revenue from rendering of services</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n"/>
-      <c r="C26" s="37" t="n"/>
+      <c r="B26" s="37">
+        <f>1*B18+1*B19+1*B20+1*B21+1*B22+1*B23+1*B24+1*B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="37">
+        <f>1*C18+1*C19+1*C20+1*C21+1*C22+1*C23+1*C24+1*C25</f>
+        <v/>
+      </c>
       <c r="D26" s="38" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="10">
@@ -1373,8 +1397,14 @@
           <t>Interest income</t>
         </is>
       </c>
-      <c r="B30" s="37" t="n"/>
-      <c r="C30" s="37" t="n"/>
+      <c r="B30" s="37">
+        <f>1*B28+1*B29</f>
+        <v/>
+      </c>
+      <c r="C30" s="37">
+        <f>1*C28+1*C29</f>
+        <v/>
+      </c>
       <c r="D30" s="38" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="10">
@@ -1424,11 +1454,11 @@
         </is>
       </c>
       <c r="B35" s="28">
-        <f>1*B20+1*B21+1*B22+1*B23+1*B24+1*B25+1*B26+1*B28+1*B29+1*B30+1*B32+1*B33+1*B34</f>
+        <f>1*B32+1*B33+1*B34</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>1*C20+1*C21+1*C22+1*C23+1*C24+1*C25+1*C26+1*C28+1*C29+1*C30+1*C32+1*C33+1*C34</f>
+        <f>1*C32+1*C33+1*C34</f>
         <v/>
       </c>
       <c r="D35" s="33" t="n"/>
@@ -1480,11 +1510,11 @@
         </is>
       </c>
       <c r="B40" s="35">
-        <f>1*B36+1*B37+1*B38+1*B39</f>
+        <f>1*B16+1*B26+1*B30+1*B35+1*B36+1*B37+1*B38+1*B39</f>
         <v/>
       </c>
       <c r="C40" s="35">
-        <f>1*C36+1*C37+1*C38+1*C39</f>
+        <f>1*C16+1*C26+1*C30+1*C35+1*C36+1*C37+1*C38+1*C39</f>
         <v/>
       </c>
       <c r="D40" s="36" t="n"/>
@@ -1645,8 +1675,14 @@
           <t>Gains on foreign exchange</t>
         </is>
       </c>
-      <c r="B56" s="37" t="n"/>
-      <c r="C56" s="37" t="n"/>
+      <c r="B56" s="37">
+        <f>1*B54+1*B55</f>
+        <v/>
+      </c>
+      <c r="C56" s="37">
+        <f>1*C54+1*C55</f>
+        <v/>
+      </c>
       <c r="D56" s="38" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1" s="10">
@@ -1695,8 +1731,14 @@
           <t>Gain from disposal of a subsidiary, joint ventures and associates</t>
         </is>
       </c>
-      <c r="B61" s="30" t="n"/>
-      <c r="C61" s="30" t="n"/>
+      <c r="B61" s="30">
+        <f>1*B58+1*B59+1*B60</f>
+        <v/>
+      </c>
+      <c r="C61" s="30">
+        <f>1*C58+1*C59+1*C60</f>
+        <v/>
+      </c>
       <c r="D61" s="34" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1" s="10">
@@ -1805,8 +1847,14 @@
           <t>Reversal of impairment loss recognised in profit or loss</t>
         </is>
       </c>
-      <c r="B72" s="30" t="n"/>
-      <c r="C72" s="30" t="n"/>
+      <c r="B72" s="30">
+        <f>1*B67+1*B68+1*B69+1*B70+1*B71</f>
+        <v/>
+      </c>
+      <c r="C72" s="30">
+        <f>1*C67+1*C68+1*C69+1*C70+1*C71</f>
+        <v/>
+      </c>
       <c r="D72" s="34" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1" s="10">
@@ -1915,8 +1963,14 @@
           <t>Other income</t>
         </is>
       </c>
-      <c r="B83" s="37" t="n"/>
-      <c r="C83" s="37" t="n"/>
+      <c r="B83" s="37">
+        <f>1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49+1*B50+1*B51+1*B52+1*B56+1*B61+1*B62+1*B63+1*B64+1*B65+1*B72+1*B73+1*B74+1*B75+1*B76+1*B77+1*B78+1*B79+1*B80+1*B81+1*B82</f>
+        <v/>
+      </c>
+      <c r="C83" s="37">
+        <f>1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49+1*C50+1*C51+1*C52+1*C56+1*C61+1*C62+1*C63+1*C64+1*C65+1*C72+1*C73+1*C74+1*C75+1*C76+1*C77+1*C78+1*C79+1*C80+1*C81+1*C82</f>
+        <v/>
+      </c>
       <c r="D83" s="38" t="n"/>
     </row>
     <row r="84" ht="18" customHeight="1" s="10">
@@ -1985,14 +2039,8 @@
           <t>Total post-employment benefit expense in profit or loss, defined benefit plans</t>
         </is>
       </c>
-      <c r="B90" s="28">
-        <f>1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49+1*B50+1*B51+1*B52+1*B54+1*B55+1*B56+1*B58+1*B59+1*B60+1*B61+1*B62+1*B63+1*B64+1*B65+1*B67+1*B68+1*B69+1*B70+1*B71+1*B72+1*B73+1*B74+1*B75+1*B76+1*B77+1*B78+1*B79+1*B80+1*B81+1*B82+1*B83+1*B85+1*B86+1*B87+1*B88+1*B89</f>
-        <v/>
-      </c>
-      <c r="C90" s="28">
-        <f>1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49+1*C50+1*C51+1*C52+1*C54+1*C55+1*C56+1*C58+1*C59+1*C60+1*C61+1*C62+1*C63+1*C64+1*C65+1*C67+1*C68+1*C69+1*C70+1*C71+1*C72+1*C73+1*C74+1*C75+1*C76+1*C77+1*C78+1*C79+1*C80+1*C81+1*C82+1*C83+1*C85+1*C86+1*C87+1*C88+1*C89</f>
-        <v/>
-      </c>
+      <c r="B90" s="28" t="n"/>
+      <c r="C90" s="28" t="n"/>
       <c r="D90" s="33" t="n"/>
     </row>
     <row r="91" ht="18" customHeight="1" s="10">
@@ -2042,11 +2090,11 @@
         </is>
       </c>
       <c r="B95" s="35">
-        <f>1*B91+1*B92+1*B93+1*B94</f>
+        <f>1*B85+1*B86+1*B87+1*B88+1*B89+1*B90+1*B91+1*B92+1*B93+1*B94</f>
         <v/>
       </c>
       <c r="C95" s="35">
-        <f>1*C91+1*C92+1*C93+1*C94</f>
+        <f>1*C85+1*C86+1*C87+1*C88+1*C89+1*C90+1*C91+1*C92+1*C93+1*C94</f>
         <v/>
       </c>
       <c r="D95" s="36" t="n"/>
@@ -2183,8 +2231,14 @@
           <t>Loss on disposal of subsidiaries, joint ventures and associates</t>
         </is>
       </c>
-      <c r="B108" s="30" t="n"/>
-      <c r="C108" s="30" t="n"/>
+      <c r="B108" s="30">
+        <f>1*B105+1*B106+1*B107</f>
+        <v/>
+      </c>
+      <c r="C108" s="30">
+        <f>1*C105+1*C106+1*C107</f>
+        <v/>
+      </c>
       <c r="D108" s="34" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1" s="10">
@@ -2363,8 +2417,14 @@
           <t>Director's remuneration</t>
         </is>
       </c>
-      <c r="B126" s="30" t="n"/>
-      <c r="C126" s="30" t="n"/>
+      <c r="B126" s="30">
+        <f>1*B117+1*B118+1*B119+1*B120+1*B121+1*B122+1*B123+1*B124+1*B125</f>
+        <v/>
+      </c>
+      <c r="C126" s="30">
+        <f>1*C117+1*C118+1*C119+1*C120+1*C121+1*C122+1*C123+1*C124+1*C125</f>
+        <v/>
+      </c>
       <c r="D126" s="34" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1" s="10">
@@ -2383,8 +2443,14 @@
           <t>Other expenses, by nature</t>
         </is>
       </c>
-      <c r="B128" s="37" t="n"/>
-      <c r="C128" s="37" t="n"/>
+      <c r="B128" s="37">
+        <f>1*B100+1*B101+1*B102+1*B103+1*B108+1*B109+1*B110+1*B111+1*B112+1*B113+1*B114+1*B115+1*B126+1*B127</f>
+        <v/>
+      </c>
+      <c r="C128" s="37">
+        <f>1*C100+1*C101+1*C102+1*C103+1*C108+1*C109+1*C110+1*C111+1*C112+1*C113+1*C114+1*C115+1*C126+1*C127</f>
+        <v/>
+      </c>
       <c r="D128" s="38" t="n"/>
     </row>
     <row r="129" ht="18" customHeight="1" s="10">
@@ -2423,8 +2489,14 @@
           <t>Finance income</t>
         </is>
       </c>
-      <c r="B132" s="30" t="n"/>
-      <c r="C132" s="30" t="n"/>
+      <c r="B132" s="30">
+        <f>1*B130+1*B131</f>
+        <v/>
+      </c>
+      <c r="C132" s="30">
+        <f>1*C130+1*C131</f>
+        <v/>
+      </c>
       <c r="D132" s="34" t="n"/>
     </row>
   </sheetData>
